--- a/L-shaped/Final_codes/data/Starting_point.xlsx
+++ b/L-shaped/Final_codes/data/Starting_point.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fthcn\Desktop\Vaccine_Tender_Scheduling_Problem\Julia_Files\L-shaped method\Using_deterministic_model_from_IISE_paper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/L-shaped/Final_codes/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D97F6FD3-B23A-4A36-A445-5D1855D05295}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13550" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -557,9 +557,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942AD6D9-E2BE-4540-AD66-B6783F716305}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -570,7 +574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -581,7 +585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -592,7 +596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -603,7 +607,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -614,7 +618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -625,7 +629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -636,7 +640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -647,7 +651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -658,7 +662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -669,7 +673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -680,7 +684,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -691,7 +695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -711,15 +715,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E851515-DB43-462D-9C92-F50748C0A12A}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="8.85546875" style="2"/>
     <col min="2" max="2" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.88671875" style="2"/>
-    <col min="5" max="5" width="16.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.85546875" style="2"/>
+    <col min="5" max="5" width="16.140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -736,7 +740,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -753,7 +757,7 @@
         <v>13299</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -770,7 +774,7 @@
         <v>12505</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -787,7 +791,7 @@
         <v>13547</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -804,7 +808,7 @@
         <v>6547</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -821,7 +825,7 @@
         <v>90279</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
@@ -838,7 +842,7 @@
         <v>180177</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -855,7 +859,7 @@
         <v>13305</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -872,7 +876,7 @@
         <v>8948</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -889,7 +893,7 @@
         <v>140932</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
@@ -906,7 +910,7 @@
         <v>17896</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -923,7 +927,7 @@
         <v>31318</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
@@ -940,7 +944,7 @@
         <v>53688</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -957,7 +961,7 @@
         <v>43365</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -974,7 +978,7 @@
         <v>40214</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
@@ -991,7 +995,7 @@
         <v>219201</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>34</v>
       </c>
@@ -1008,7 +1012,7 @@
         <v>61221</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
@@ -1025,7 +1029,7 @@
         <v>84681</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -1042,7 +1046,7 @@
         <v>3625</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
@@ -1059,7 +1063,7 @@
         <v>13464</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
@@ -1076,7 +1080,7 @@
         <v>5391</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>10</v>
       </c>
@@ -1093,7 +1097,7 @@
         <v>56510</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -1110,7 +1114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -1127,7 +1131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>13</v>
       </c>
@@ -1144,7 +1148,7 @@
         <v>185663</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>13</v>
       </c>
@@ -1161,7 +1165,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>13</v>
       </c>
@@ -1187,13 +1191,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF8CA8F-1DBE-42B3-8633-48C2ED5062E9}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1201,7 +1205,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1209,7 +1213,7 @@
         <v>137010500</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -1217,7 +1221,7 @@
         <v>283717500</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1225,7 +1229,7 @@
         <v>9879500</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1233,7 +1237,7 @@
         <v>108804000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1241,7 +1245,7 @@
         <v>46674000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1249,7 +1253,7 @@
         <v>143467000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1257,7 +1261,7 @@
         <v>11463500</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -1265,7 +1269,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>40</v>
       </c>
@@ -1273,7 +1277,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>7</v>
       </c>
@@ -1281,7 +1285,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
@@ -1289,7 +1293,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>27</v>
       </c>
@@ -1297,7 +1301,7 @@
         <v>143856000</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>42</v>
       </c>
@@ -1305,7 +1309,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>43</v>
       </c>
@@ -1313,7 +1317,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>44</v>
       </c>
@@ -1321,7 +1325,7 @@
         <v>43714500</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
@@ -1329,7 +1333,7 @@
         <v>9216211.8592507206</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>10</v>
       </c>
@@ -1346,13 +1350,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903BEB0C-00BA-4B81-9CB6-933B54D27020}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>45</v>
       </c>
@@ -1360,7 +1364,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1368,7 +1372,7 @@
         <v>109769715.256769</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1376,7 +1380,7 @@
         <v>76483381.4640522</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1384,7 +1388,7 @@
         <v>111936141.058823</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -1392,7 +1396,7 @@
         <v>6763202.4705882296</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1400,7 +1404,7 @@
         <v>50081880.540420704</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1408,7 +1412,7 @@
         <v>59034355.4808589</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1416,7 +1420,7 @@
         <v>171888397.557423</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1424,7 +1428,7 @@
         <v>52857961.247619003</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
@@ -1432,7 +1436,7 @@
         <v>63880730.2712842</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1440,7 +1444,7 @@
         <v>106632842.278244</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1448,7 +1452,7 @@
         <v>148000000</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>

--- a/L-shaped/Final_codes/data/Starting_point.xlsx
+++ b/L-shaped/Final_codes/data/Starting_point.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/L-shaped/Final_codes/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Model objective analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D97F6FD3-B23A-4A36-A445-5D1855D05295}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBD7E713-1AF3-4E4D-91B0-05E744E35DB1}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13550" yWindow="-7070" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -254,7 +254,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -273,7 +273,8 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -558,10 +559,6 @@
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1210,7 +1207,7 @@
         <v>29</v>
       </c>
       <c r="B2" s="8">
-        <v>137010500</v>
+        <v>398056107.80000001</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1218,7 +1215,7 @@
         <v>34</v>
       </c>
       <c r="B3" s="8">
-        <v>283717500</v>
+        <v>27968660.210000001</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1226,7 +1223,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="8">
-        <v>9879500</v>
+        <v>410128001.42000002</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1234,31 +1231,31 @@
         <v>13</v>
       </c>
       <c r="B5" s="8">
-        <v>108804000</v>
+        <v>590379508</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="8">
-        <v>46674000</v>
+      <c r="B6" s="9">
+        <v>280763726</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="8">
-        <v>143467000</v>
+      <c r="B7" s="9">
+        <v>879375105</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="8">
-        <v>11463500</v>
+      <c r="B8" s="9">
+        <v>83171840</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1266,7 +1263,7 @@
         <v>39</v>
       </c>
       <c r="B9" s="8">
-        <v>10000000</v>
+        <v>7682600</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1274,7 +1271,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="8">
-        <v>10000000</v>
+        <v>3278988.3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1282,7 +1279,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="8">
-        <v>10000000</v>
+        <v>2828944.58</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1290,7 +1287,7 @@
         <v>41</v>
       </c>
       <c r="B12" s="8">
-        <v>10000000</v>
+        <v>116834378.34999999</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1298,7 +1295,7 @@
         <v>27</v>
       </c>
       <c r="B13" s="8">
-        <v>143856000</v>
+        <v>5298997.59</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1306,7 +1303,7 @@
         <v>42</v>
       </c>
       <c r="B14" s="8">
-        <v>10000000</v>
+        <v>30290394.390000001</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1314,7 +1311,7 @@
         <v>43</v>
       </c>
       <c r="B15" s="8">
-        <v>10000000</v>
+        <v>43271991.979999997</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1322,7 +1319,7 @@
         <v>44</v>
       </c>
       <c r="B16" s="8">
-        <v>43714500</v>
+        <v>86543983.959999993</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1330,7 +1327,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="8">
-        <v>9216211.8592507206</v>
+        <v>242285505</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1338,7 +1335,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="8">
-        <v>67456638.140749902</v>
+        <v>156726900</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1350,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1369,7 +1366,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="7">
-        <v>109769715.256769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1377,7 +1374,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="7">
-        <v>76483381.4640522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1385,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="7">
-        <v>111936141.058823</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1393,7 +1390,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="7">
-        <v>6763202.4705882296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1401,7 +1398,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="7">
-        <v>50081880.540420704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1409,7 +1406,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="7">
-        <v>59034355.4808589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1417,7 +1414,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="7">
-        <v>171888397.557423</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1425,7 +1422,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="7">
-        <v>52857961.247619003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1433,7 +1430,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="7">
-        <v>63880730.2712842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1441,7 +1438,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="7">
-        <v>106632842.278244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1449,7 +1446,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="7">
-        <v>148000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1457,7 +1454,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="7">
-        <v>21600000</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/L-shaped/Final_codes/data/Starting_point.xlsx
+++ b/L-shaped/Final_codes/data/Starting_point.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Model objective analysis/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/L-shaped/Final_codes/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBD7E713-1AF3-4E4D-91B0-05E744E35DB1}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57B689CC-C146-43A4-977D-6601980C66FA}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-7070" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13550" yWindow="-7070" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -186,10 +186,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.00000E+00"/>
-    <numFmt numFmtId="165" formatCode="0.000000E+00"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -254,7 +253,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -273,8 +272,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1191,7 +1189,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1238,7 +1236,7 @@
       <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>280763726</v>
       </c>
     </row>
@@ -1246,7 +1244,7 @@
       <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <v>879375105</v>
       </c>
     </row>
@@ -1254,7 +1252,7 @@
       <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <v>83171840</v>
       </c>
     </row>

--- a/L-shaped/Final_codes/data/Starting_point.xlsx
+++ b/L-shaped/Final_codes/data/Starting_point.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/L-shaped/Final_codes/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57B689CC-C146-43A4-977D-6601980C66FA}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA018D63-BB8A-4AEE-BBEF-E7241FAD85B4}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-7070" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="46">
   <si>
     <t>Measles</t>
   </si>
@@ -176,10 +176,7 @@
     <t>Hexa</t>
   </si>
   <si>
-    <t>antigen</t>
-  </si>
-  <si>
-    <t>Unvaccinated Children</t>
+    <t>Unvaccinated_Children</t>
   </si>
 </sst>
 </file>
@@ -289,6 +286,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1353,10 +1354,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
